--- a/src/assets/updateBill.xlsx
+++ b/src/assets/updateBill.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bills Report" sheetId="1" state="visible" r:id="rId1"/>
